--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_4.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_4.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_0</t>
+          <t>model_23_4_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9804282246118234</v>
+        <v>0.9999694962536958</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7104571844686787</v>
+        <v>0.7130239003152472</v>
       </c>
       <c r="D2" t="n">
-        <v>0.99892257093255</v>
+        <v>0.9999796033197815</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9942879825223677</v>
+        <v>0.9998312271524187</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9958359981850239</v>
+        <v>0.9999333416201619</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01161865132709612</v>
+        <v>1.810834149940538e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.171885122897763</v>
+        <v>0.1703614094948886</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001738893280220232</v>
+        <v>2.242275278521006e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002782705615094068</v>
+        <v>8.993623758191e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001478297316027578</v>
+        <v>5.617983051170575e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03085503079605554</v>
+        <v>0.001523238980364819</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1077898479778876</v>
+        <v>0.004255389700063366</v>
       </c>
       <c r="N2" t="n">
-        <v>1.009033127102235</v>
+        <v>1.00001407865214</v>
       </c>
       <c r="O2" t="n">
-        <v>0.112378684962052</v>
+        <v>0.004436550449466119</v>
       </c>
       <c r="P2" t="n">
-        <v>160.9102871981764</v>
+        <v>173.8382757390668</v>
       </c>
       <c r="Q2" t="n">
-        <v>253.5448498881597</v>
+        <v>266.4728384290501</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_1</t>
+          <t>model_23_4_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9830663608607836</v>
+        <v>0.9999699360843106</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7040415321929829</v>
+        <v>0.7129870669608143</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9968763592238681</v>
+        <v>0.999979799152007</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9878753450928193</v>
+        <v>0.9998342455465209</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9909710853179042</v>
+        <v>0.9999344239663155</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01005253968816132</v>
+        <v>1.784723904674368e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1756937312303637</v>
+        <v>0.170383275365198</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005041332296976972</v>
+        <v>2.220746786957093e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005906730051756666</v>
+        <v>8.832778567166737e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003205430961432138</v>
+        <v>5.526762677061915e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03046178716508889</v>
+        <v>0.001524530573176809</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1002623542919341</v>
+        <v>0.004224599276469152</v>
       </c>
       <c r="N3" t="n">
-        <v>1.007815525756562</v>
+        <v>1.000013875653395</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1045307302858274</v>
+        <v>0.004404449213794536</v>
       </c>
       <c r="P3" t="n">
-        <v>161.199859942224</v>
+        <v>173.8673234739091</v>
       </c>
       <c r="Q3" t="n">
-        <v>253.8344226322072</v>
+        <v>266.5018861638923</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_2</t>
+          <t>model_23_4_22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.984743464536614</v>
+        <v>0.9999704132471002</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6974652794084565</v>
+        <v>0.7129461491061264</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9943875652610638</v>
+        <v>0.9999800146913941</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9794693096816779</v>
+        <v>0.9998375679846621</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9846378693088237</v>
+        <v>0.9999356148872225</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009056938499081861</v>
+        <v>1.756397460246933e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1795976789625872</v>
+        <v>0.1704075659713</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009058067345731305</v>
+        <v>2.197051821204009e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01000187192253381</v>
+        <v>8.655731376048624e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005453839258079402</v>
+        <v>5.426391598626317e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03009490704972502</v>
+        <v>0.001525905373265368</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0951679489065613</v>
+        <v>0.004190939584683764</v>
       </c>
       <c r="N4" t="n">
-        <v>1.007041477906178</v>
+        <v>1.000013655424415</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09921944551632629</v>
+        <v>0.004369356559244677</v>
       </c>
       <c r="P4" t="n">
-        <v>161.4084482600834</v>
+        <v>173.8993213025302</v>
       </c>
       <c r="Q4" t="n">
-        <v>254.0430109500666</v>
+        <v>266.5338839925134</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_3</t>
+          <t>model_23_4_21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9856485723825783</v>
+        <v>0.9999709287184086</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6908469070559089</v>
+        <v>0.712900685044192</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9917995689706556</v>
+        <v>0.9999802531425356</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9694039148584422</v>
+        <v>0.9998412134512668</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9771435946743134</v>
+        <v>0.999936923422586</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008519627383094353</v>
+        <v>1.725796856661006e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1835266306898585</v>
+        <v>0.1704345554024095</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001323490783999818</v>
+        <v>2.170838089664974e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01490539870662322</v>
+        <v>8.461470536488416e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008114444745311519</v>
+        <v>5.316107947691173e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02975676129987781</v>
+        <v>0.001527399146252061</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0923018276259704</v>
+        <v>0.004154271123387358</v>
       </c>
       <c r="N5" t="n">
-        <v>1.006623735823425</v>
+        <v>1.000013417514581</v>
       </c>
       <c r="O5" t="n">
-        <v>0.09623130751913168</v>
+        <v>0.004331127045636703</v>
       </c>
       <c r="P5" t="n">
-        <v>161.5307653469518</v>
+        <v>173.9344731505213</v>
       </c>
       <c r="Q5" t="n">
-        <v>254.165328036935</v>
+        <v>266.5690358405045</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_4</t>
+          <t>model_23_4_20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9859395901848995</v>
+        <v>0.9999714865730558</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6842898299110585</v>
+        <v>0.7128502026194254</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9893133239069567</v>
+        <v>0.9999805155330617</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9580148192429977</v>
+        <v>0.999845232281137</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9687642388326616</v>
+        <v>0.9999383642308168</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008346866644321986</v>
+        <v>1.692680194998422e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1874191949340257</v>
+        <v>0.1704645239504781</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001724752914831199</v>
+        <v>2.141992621486588e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02045378864836377</v>
+        <v>8.247313790785317e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01108927035806761</v>
+        <v>5.194676310136105e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02945091124568905</v>
+        <v>0.00152902674817234</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09136118784430282</v>
+        <v>0.004114219482475895</v>
       </c>
       <c r="N6" t="n">
-        <v>1.006489419914662</v>
+        <v>1.000013160043205</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09525062275456572</v>
+        <v>0.004289370323453313</v>
       </c>
       <c r="P6" t="n">
-        <v>161.5717381254422</v>
+        <v>173.9732245561378</v>
       </c>
       <c r="Q6" t="n">
-        <v>254.2063008154254</v>
+        <v>266.6077872461211</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_5</t>
+          <t>model_23_4_19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9857488087719956</v>
+        <v>0.9999720795700717</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6778790528062244</v>
+        <v>0.7127941459821131</v>
       </c>
       <c r="D7" t="n">
-        <v>0.987032953231215</v>
+        <v>0.9999808004793659</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9456292654203461</v>
+        <v>0.9998496102120996</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9597479890072068</v>
+        <v>0.9999399336679476</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00846012273234968</v>
+        <v>1.657477330522045e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1912249091546066</v>
+        <v>0.1704978015919074</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002092788395240438</v>
+        <v>2.110667521194221e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02648762000537655</v>
+        <v>8.014021146376032e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01429020506219437</v>
+        <v>5.062403800326752e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02919283628474965</v>
+        <v>0.00153095734594822</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09197892547942534</v>
+        <v>0.004071212756074098</v>
       </c>
       <c r="N7" t="n">
-        <v>1.006577472874464</v>
+        <v>1.000012886352275</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0958946587597086</v>
+        <v>0.004244532711672394</v>
       </c>
       <c r="P7" t="n">
-        <v>161.5447831961986</v>
+        <v>174.0152573977913</v>
       </c>
       <c r="Q7" t="n">
-        <v>254.1793458861819</v>
+        <v>266.6498200877746</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_6</t>
+          <t>model_23_4_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9851871704405433</v>
+        <v>0.9999727157703554</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6716821967596329</v>
+        <v>0.7127316695266681</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9850013187677217</v>
+        <v>0.9999811149277253</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9325564001332969</v>
+        <v>0.9998544249950998</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9503167081669637</v>
+        <v>0.9999416614766325</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008793535507412398</v>
+        <v>1.619709733439959e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1949036305941061</v>
+        <v>0.1705348903147019</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002420679634038516</v>
+        <v>2.076099161275474e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03285628672989077</v>
+        <v>7.75744938497102e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01763848341853163</v>
+        <v>4.916783700782951e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02896310147583363</v>
+        <v>0.001532944727617114</v>
       </c>
       <c r="M8" t="n">
-        <v>0.09377385300504826</v>
+        <v>0.004024561756812733</v>
       </c>
       <c r="N8" t="n">
-        <v>1.006836690565903</v>
+        <v>1.000012592721374</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09776600006610948</v>
+        <v>0.004195895682791592</v>
       </c>
       <c r="P8" t="n">
-        <v>161.4674768577605</v>
+        <v>174.0613570173379</v>
       </c>
       <c r="Q8" t="n">
-        <v>254.1020395477437</v>
+        <v>266.6959197073211</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_7</t>
+          <t>model_23_4_17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9843472454712876</v>
+        <v>0.9999733866059419</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6657499510934096</v>
+        <v>0.712662316417243</v>
       </c>
       <c r="D9" t="n">
-        <v>0.983223064975787</v>
+        <v>0.9999814548466416</v>
       </c>
       <c r="E9" t="n">
-        <v>0.919077547166096</v>
+        <v>0.9998596713805713</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9406644632195562</v>
+        <v>0.9999435418609561</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009292151252032038</v>
+        <v>1.579886035161475e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1984252678812458</v>
+        <v>0.1705760613163549</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002707677048786149</v>
+        <v>2.038730737868883e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03942273719747669</v>
+        <v>7.477878247211611e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02106520810152144</v>
+        <v>4.758304492540246e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02876100577206188</v>
+        <v>0.001535347120080616</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09639580515785963</v>
+        <v>0.003974778025451831</v>
       </c>
       <c r="N9" t="n">
-        <v>1.007224348244021</v>
+        <v>1.00001228310495</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1004995741502552</v>
+        <v>0.004143992554920125</v>
       </c>
       <c r="P9" t="n">
-        <v>161.3571703730896</v>
+        <v>174.1111455003549</v>
       </c>
       <c r="Q9" t="n">
-        <v>253.9917330630729</v>
+        <v>266.7457081903382</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_8</t>
+          <t>model_23_4_16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9833057620958957</v>
+        <v>0.9999740923197872</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6601175455437724</v>
+        <v>0.7125851295740931</v>
       </c>
       <c r="D10" t="n">
-        <v>0.981683162588884</v>
+        <v>0.999981828607992</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9054408002835946</v>
+        <v>0.999865388315443</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9309580684507854</v>
+        <v>0.9999455925867942</v>
       </c>
       <c r="G10" t="n">
-        <v>0.009910420773403896</v>
+        <v>1.537991812781895e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2017689071227614</v>
+        <v>0.1706218827607467</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002956206255364756</v>
+        <v>1.997641902467318e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04606610834788901</v>
+        <v>7.173232316165633e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0245111569681552</v>
+        <v>4.58546886364258e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02858558612954736</v>
+        <v>0.001537804618879525</v>
       </c>
       <c r="M10" t="n">
-        <v>0.09955109629433469</v>
+        <v>0.003921723871949548</v>
       </c>
       <c r="N10" t="n">
-        <v>1.007705032878817</v>
+        <v>1.000011957390867</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1037891925627631</v>
+        <v>0.004088679776266012</v>
       </c>
       <c r="P10" t="n">
-        <v>161.2283369441319</v>
+        <v>174.1648958343794</v>
       </c>
       <c r="Q10" t="n">
-        <v>253.8628996341151</v>
+        <v>266.7994585243626</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_9</t>
+          <t>model_23_4_15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9821261184234202</v>
+        <v>0.9999748255222092</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6548075225251524</v>
+        <v>0.7124994843048927</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9803558293588642</v>
+        <v>0.9999822338057462</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8918609710180159</v>
+        <v>0.9998715995211522</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9213390504176107</v>
+        <v>0.9999478208263759</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01061070821533866</v>
+        <v>1.494465749743166e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.204921166167665</v>
+        <v>0.170672725492227</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00317042832380746</v>
+        <v>1.953097158055691e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.05268175112162383</v>
+        <v>6.8422475159821e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02792608548478568</v>
+        <v>4.397672337018896e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02843541449909577</v>
+        <v>0.001540618243994617</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1030082919736982</v>
+        <v>0.003865832057582386</v>
       </c>
       <c r="N11" t="n">
-        <v>1.008249483804575</v>
+        <v>1.00001161898975</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1073935682195788</v>
+        <v>0.004030408531649234</v>
       </c>
       <c r="P11" t="n">
-        <v>161.0917831575752</v>
+        <v>174.222313360053</v>
       </c>
       <c r="Q11" t="n">
-        <v>253.7263458475585</v>
+        <v>266.8568760500362</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_10</t>
+          <t>model_23_4_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9808597950817938</v>
+        <v>0.9999755764633513</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6498317121433177</v>
+        <v>0.7124041658603371</v>
       </c>
       <c r="D12" t="n">
-        <v>0.979212782741011</v>
+        <v>0.9999826703820688</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8785156090895822</v>
+        <v>0.9998783271967505</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9119227715097005</v>
+        <v>0.9999502325318286</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01136245245324815</v>
+        <v>1.449886639648793e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2078750221541386</v>
+        <v>0.1707293106384577</v>
       </c>
       <c r="I12" t="n">
-        <v>0.003354907854090376</v>
+        <v>1.905102862676342e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05918316917910305</v>
+        <v>6.483740896195699e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.03126903787891438</v>
+        <v>4.194413266058291e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02830868417389387</v>
+        <v>0.001543869057172798</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1065948050012202</v>
+        <v>0.003807737700589148</v>
       </c>
       <c r="N12" t="n">
-        <v>1.00883394073148</v>
+        <v>1.00001127240153</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1111327665317878</v>
+        <v>0.003969840977606896</v>
       </c>
       <c r="P12" t="n">
-        <v>160.9548820080398</v>
+        <v>174.282880182293</v>
       </c>
       <c r="Q12" t="n">
-        <v>253.5894446980231</v>
+        <v>266.9174428722762</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_11</t>
+          <t>model_23_4_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9795482447366514</v>
+        <v>0.9999763334315996</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6451937501672089</v>
+        <v>0.7122982340908139</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9782267595283637</v>
+        <v>0.9999831428872251</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8655484148370791</v>
+        <v>0.9998855860011857</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9028016574471562</v>
+        <v>0.9999528351112511</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01214104539414956</v>
+        <v>1.404949734498671e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2106283167326821</v>
+        <v>0.1707921963128608</v>
       </c>
       <c r="I13" t="n">
-        <v>0.003514044932382821</v>
+        <v>1.853158790427101e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.06550035647759382</v>
+        <v>6.096931305910617e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.03450720131807167</v>
+        <v>3.975067294543931e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02820326702434084</v>
+        <v>0.001547372369233112</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1101864120213993</v>
+        <v>0.003748265911723274</v>
       </c>
       <c r="N13" t="n">
-        <v>1.009439271660007</v>
+        <v>1.000010923031569</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1148772756984674</v>
+        <v>0.003907837351565428</v>
       </c>
       <c r="P13" t="n">
-        <v>160.8223267710275</v>
+        <v>174.345847877964</v>
       </c>
       <c r="Q13" t="n">
-        <v>253.4568894610107</v>
+        <v>266.9804105679473</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9782243481502152</v>
+        <v>0.9999770805435885</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6408902239471708</v>
+        <v>0.7121804774841389</v>
       </c>
       <c r="D14" t="n">
-        <v>0.977371466767876</v>
+        <v>0.9999836499275888</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8530713273946214</v>
+        <v>0.9998933972579021</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8940465383318847</v>
+        <v>0.9999556353997288</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01292696759721283</v>
+        <v>1.360597939482173e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2131830757995496</v>
+        <v>0.1708621017214036</v>
       </c>
       <c r="I14" t="n">
-        <v>0.003652083052827543</v>
+        <v>1.797418147311855e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.07157877998069187</v>
+        <v>5.680682454317067e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03761542981188704</v>
+        <v>3.739058359968856e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02811697429516231</v>
+        <v>0.001551258387971273</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1136968231623594</v>
+        <v>0.003688628389363956</v>
       </c>
       <c r="N14" t="n">
-        <v>1.010050300853747</v>
+        <v>1.000010578210651</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1185371323092511</v>
+        <v>0.003845660936412584</v>
       </c>
       <c r="P14" t="n">
-        <v>160.6968792765621</v>
+        <v>174.4100024009221</v>
       </c>
       <c r="Q14" t="n">
-        <v>253.3314419665454</v>
+        <v>267.0445650909054</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_13</t>
+          <t>model_23_4_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9769135676647827</v>
+        <v>0.9999777907567888</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6369128688538117</v>
+        <v>0.7120496156108946</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9766262438784908</v>
+        <v>0.9999841930017815</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8411661322541142</v>
+        <v>0.9999017335363632</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8857088041170733</v>
+        <v>0.9999586250956155</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01370510351613424</v>
+        <v>1.31843661595335e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2155442055957615</v>
+        <v>0.1709397869823001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.003772356685103406</v>
+        <v>1.737716184847827e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.07737859650716594</v>
+        <v>5.236456068985537e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.04057547898073628</v>
+        <v>3.487086126916681e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02804756104807645</v>
+        <v>0.001555624880688673</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1170687982176901</v>
+        <v>0.003631028250996335</v>
       </c>
       <c r="N15" t="n">
-        <v>1.010655276462408</v>
+        <v>1.000010250419944</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1220526593236379</v>
+        <v>0.003785608640905929</v>
       </c>
       <c r="P15" t="n">
-        <v>160.5799739921807</v>
+        <v>174.4729576243199</v>
       </c>
       <c r="Q15" t="n">
-        <v>253.2145366821639</v>
+        <v>267.1075203143031</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_14</t>
+          <t>model_23_4_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9756353381203631</v>
+        <v>0.9999784359749809</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6332494232077326</v>
+        <v>0.7119041368343949</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9759722711820068</v>
+        <v>0.9999847721427698</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8298905281971027</v>
+        <v>0.9999106045930237</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8778237946182648</v>
+        <v>0.9999618072818832</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01446391579034297</v>
+        <v>1.280133676872163e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2177189851838859</v>
+        <v>0.1710261494683862</v>
       </c>
       <c r="I16" t="n">
-        <v>0.003877903190364767</v>
+        <v>1.674049278919579e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.08287169712282258</v>
+        <v>4.763732244711826e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.04337480253939027</v>
+        <v>3.218890761815702e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02799237138737464</v>
+        <v>0.001560358190866445</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1202660209300323</v>
+        <v>0.003577895578230537</v>
       </c>
       <c r="N16" t="n">
-        <v>1.011245228559832</v>
+        <v>1.000009952626932</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1253859944260079</v>
+        <v>0.003730214000260696</v>
       </c>
       <c r="P16" t="n">
-        <v>160.472196594733</v>
+        <v>174.5319219148706</v>
       </c>
       <c r="Q16" t="n">
-        <v>253.1067592847162</v>
+        <v>267.1664846048538</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_15</t>
+          <t>model_23_4_9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9744037011866123</v>
+        <v>0.9999789709664271</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6298853226550076</v>
+        <v>0.7117424083823219</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9753948328746429</v>
+        <v>0.9999853806534634</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8192782034698243</v>
+        <v>0.9999199557127937</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8704112814307861</v>
+        <v>0.9999651610618346</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0151950686781626</v>
+        <v>1.248374273585888e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2197160605935605</v>
+        <v>0.171122158463842</v>
       </c>
       <c r="I17" t="n">
-        <v>0.003971097593852819</v>
+        <v>1.607153663036548e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08804167003054567</v>
+        <v>4.265426657445893e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.04600638120745373</v>
+        <v>2.93623344295648e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02794929267288223</v>
+        <v>0.00156926897133086</v>
       </c>
       <c r="M17" t="n">
-        <v>0.123268279286127</v>
+        <v>0.003533234033553238</v>
       </c>
       <c r="N17" t="n">
-        <v>1.01181367637541</v>
+        <v>1.000009705707803</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1285160651358531</v>
+        <v>0.003683651121164341</v>
       </c>
       <c r="P17" t="n">
-        <v>160.3735686656733</v>
+        <v>174.582166682554</v>
       </c>
       <c r="Q17" t="n">
-        <v>253.0081313556566</v>
+        <v>267.2167293725372</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_16</t>
+          <t>model_23_4_8</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9732288270068629</v>
+        <v>0.999979345442131</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6268041168292936</v>
+        <v>0.7115626658878493</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9748819370417716</v>
+        <v>0.999986019988843</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8093472190729578</v>
+        <v>0.9999297356647699</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8634808821042328</v>
+        <v>0.9999686691694836</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01589252474318389</v>
+        <v>1.226143778153106e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2215451974728656</v>
+        <v>0.1712288613730324</v>
       </c>
       <c r="I18" t="n">
-        <v>0.004053875304625333</v>
+        <v>1.536869386349644e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.09287971650935778</v>
+        <v>3.744269316626469e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.04846680057773243</v>
+        <v>2.640569351488057e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02791624847038659</v>
+        <v>0.001581377263030448</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1260655573231003</v>
+        <v>0.003501633587560391</v>
       </c>
       <c r="N18" t="n">
-        <v>1.012355925996832</v>
+        <v>1.000009532872863</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1314324290900242</v>
+        <v>0.003650705378763638</v>
       </c>
       <c r="P18" t="n">
-        <v>160.2838128444909</v>
+        <v>174.6181027202908</v>
       </c>
       <c r="Q18" t="n">
-        <v>252.9183755344741</v>
+        <v>267.2526654102741</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_17</t>
+          <t>model_23_4_7</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.972117045681871</v>
+        <v>0.9999794884600062</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6239882852855401</v>
+        <v>0.7113626956426694</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9744234698723557</v>
+        <v>0.9999866802917348</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8000977252194751</v>
+        <v>0.9999398546327718</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8570304690034558</v>
+        <v>0.9999722988006753</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01655252616415161</v>
+        <v>1.21765361927296e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2232167967148267</v>
+        <v>0.1713475723488361</v>
       </c>
       <c r="I19" t="n">
-        <v>0.004127868619283685</v>
+        <v>1.464280080892345e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.09738576338047722</v>
+        <v>3.205046376834163e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.05075681599988046</v>
+        <v>2.334663228863254e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02789132659620189</v>
+        <v>0.001594716546290632</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1286566211438479</v>
+        <v>0.003489489388539475</v>
       </c>
       <c r="N19" t="n">
-        <v>1.012869055839136</v>
+        <v>1.000009466864612</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1341337998618625</v>
+        <v>0.003638044176048443</v>
       </c>
       <c r="P19" t="n">
-        <v>160.2024331009796</v>
+        <v>174.6319994419218</v>
       </c>
       <c r="Q19" t="n">
-        <v>252.8369957909628</v>
+        <v>267.2665621319051</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_18</t>
+          <t>model_23_4_6</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9710722147438953</v>
+        <v>0.9999793076777106</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6214199679916722</v>
+        <v>0.7111403358814973</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9740116366634299</v>
+        <v>0.9999873555952633</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7915201905136917</v>
+        <v>0.9999501496749911</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8510516793841147</v>
+        <v>0.9999759938788454</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01717278294328039</v>
+        <v>1.228385637274902e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.224741460805997</v>
+        <v>0.1714795747085094</v>
       </c>
       <c r="I20" t="n">
-        <v>0.004194335547010765</v>
+        <v>1.390041705271011e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1015644540240048</v>
+        <v>2.656440735459119e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.05287939640212173</v>
+        <v>2.023241220365065e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02787311325743477</v>
+        <v>0.001609649731793152</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1310449653488465</v>
+        <v>0.00350483328744022</v>
       </c>
       <c r="N20" t="n">
-        <v>1.013351285502818</v>
+        <v>1.000009550302595</v>
       </c>
       <c r="O20" t="n">
-        <v>0.136623820824222</v>
+        <v>0.003654041296491643</v>
       </c>
       <c r="P20" t="n">
-        <v>160.1288590709559</v>
+        <v>174.6144492953514</v>
       </c>
       <c r="Q20" t="n">
-        <v>252.7634217609392</v>
+        <v>267.2490119853347</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_19</t>
+          <t>model_23_4_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9700959035519207</v>
+        <v>0.999978690810445</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6190814597343716</v>
+        <v>0.710893060540849</v>
       </c>
       <c r="D21" t="n">
-        <v>0.973640440554042</v>
+        <v>0.999988029767826</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7835947648677767</v>
+        <v>0.9999604425429675</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8455295670941007</v>
+        <v>0.999979687532051</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01775236344128402</v>
+        <v>1.265005542891147e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2261297003258274</v>
+        <v>0.1716263680324567</v>
       </c>
       <c r="I21" t="n">
-        <v>0.004254243938176255</v>
+        <v>1.315927660505597e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1054254587448867</v>
+        <v>2.107950955858453e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0548398479436582</v>
+        <v>1.711939308182025e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02786021363152483</v>
+        <v>0.001626260337444528</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1332379954865879</v>
+        <v>0.003556691640965164</v>
       </c>
       <c r="N21" t="n">
-        <v>1.013801890668344</v>
+        <v>1.000009835010564</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1389102127951252</v>
+        <v>0.003708107367487734</v>
       </c>
       <c r="P21" t="n">
-        <v>160.0624732406059</v>
+        <v>174.5556979221364</v>
       </c>
       <c r="Q21" t="n">
-        <v>252.6970359305892</v>
+        <v>267.1902606121197</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_20</t>
+          <t>model_23_4_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.969188087125207</v>
+        <v>0.9999774909476936</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6169551319943101</v>
+        <v>0.7106180147180555</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9733050603332045</v>
+        <v>0.9999886905406078</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7762955436468895</v>
+        <v>0.9999704525812462</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8404452313146429</v>
+        <v>0.9999832830328935</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01829128248780901</v>
+        <v>1.336234578949331e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2273919803249036</v>
+        <v>0.1717896471142278</v>
       </c>
       <c r="I22" t="n">
-        <v>0.004308371901673033</v>
+        <v>1.243286698471851e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1089813974227208</v>
+        <v>1.574532699458324e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.05664488076317405</v>
+        <v>1.408909698965087e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.027851544781655</v>
+        <v>0.00164476624969401</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1352452678943297</v>
+        <v>0.003655454252140671</v>
       </c>
       <c r="N22" t="n">
-        <v>1.014220882865289</v>
+        <v>1.000010388793372</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1410029389448913</v>
+        <v>0.003811074507487772</v>
       </c>
       <c r="P22" t="n">
-        <v>160.0026613988397</v>
+        <v>174.4461396444455</v>
       </c>
       <c r="Q22" t="n">
-        <v>252.637224088823</v>
+        <v>267.0807023344288</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_21</t>
+          <t>model_23_4_3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9683473953334194</v>
+        <v>0.9999755246225428</v>
       </c>
       <c r="C23" t="n">
-        <v>0.615024337853716</v>
+        <v>0.7103121407448045</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9730002016406306</v>
+        <v>0.999989317202578</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7695917413726288</v>
+        <v>0.9999798179676666</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8357763465694927</v>
+        <v>0.9999866519923793</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01879035345140853</v>
+        <v>1.4529641339823e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2285381831327242</v>
+        <v>0.1719712271178172</v>
       </c>
       <c r="I23" t="n">
-        <v>0.004357573909299213</v>
+        <v>1.174395652044512e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1122472677223331</v>
+        <v>1.075466866170213e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.05830242081581617</v>
+        <v>1.124973045578911e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02784627887387972</v>
+        <v>0.00166511729546596</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1370779101511565</v>
+        <v>0.003811776664473274</v>
       </c>
       <c r="N23" t="n">
-        <v>1.014608894461499</v>
+        <v>1.000011296328057</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1429136005766837</v>
+        <v>0.003974051888545378</v>
       </c>
       <c r="P23" t="n">
-        <v>159.9488233102424</v>
+        <v>174.2786395296015</v>
       </c>
       <c r="Q23" t="n">
-        <v>252.5833860002257</v>
+        <v>266.9132022195848</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_22</t>
+          <t>model_23_4_2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9675718199346582</v>
+        <v>0.9999725539306424</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6132730597269505</v>
+        <v>0.709971765908733</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9727244464026865</v>
+        <v>0.9999898772159693</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7634506659288139</v>
+        <v>0.9999880628829548</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8315001907831572</v>
+        <v>0.999989624252658</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01925076851122593</v>
+        <v>1.629317237913091e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2295778174800482</v>
+        <v>0.1721732883239366</v>
       </c>
       <c r="I24" t="n">
-        <v>0.004402078827973936</v>
+        <v>1.112831506827133e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1152389961592887</v>
+        <v>6.361090720455666e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>0.05982053485676596</v>
+        <v>8.744702894363498e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0278436318752472</v>
+        <v>0.00168788954405406</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1387471387496907</v>
+        <v>0.004036480196796574</v>
       </c>
       <c r="N24" t="n">
-        <v>1.01496685233785</v>
+        <v>1.000012667416627</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1446538916924371</v>
+        <v>0.004208321515440118</v>
       </c>
       <c r="P24" t="n">
-        <v>159.9004085927683</v>
+        <v>174.0495288206982</v>
       </c>
       <c r="Q24" t="n">
-        <v>252.5349712827515</v>
+        <v>266.6840915106814</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_23</t>
+          <t>model_23_4_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9668582580361523</v>
+        <v>0.999968291225121</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6116859318800572</v>
+        <v>0.7095930478411263</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9724734524887773</v>
+        <v>0.9999903329637186</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7578355372585348</v>
+        <v>0.9999945546736728</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8275905110196757</v>
+        <v>0.9999919742149326</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01967436967844807</v>
+        <v>1.882369851594476e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2305200051303172</v>
+        <v>0.1723981117286367</v>
       </c>
       <c r="I25" t="n">
-        <v>0.00444258744644903</v>
+        <v>1.06272963237924e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.117974500758399</v>
+        <v>2.901723643864896e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0.06120854316168431</v>
+        <v>6.764149472356954e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02784284246575127</v>
+        <v>0.001713156065587747</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1402653545193825</v>
+        <v>0.004338628644623179</v>
       </c>
       <c r="N25" t="n">
-        <v>1.015296188598699</v>
+        <v>1.000014634819175</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1462367410505846</v>
+        <v>0.004523333048224213</v>
       </c>
       <c r="P25" t="n">
-        <v>159.8568770437308</v>
+        <v>173.760787845215</v>
       </c>
       <c r="Q25" t="n">
-        <v>252.4914397337141</v>
+        <v>266.3953505351982</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_23_4_24</t>
+          <t>model_23_4_0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9662036547982814</v>
+        <v>0.999962363383236</v>
       </c>
       <c r="C26" t="n">
-        <v>0.610248979091317</v>
+        <v>0.7091715748575734</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9722456418455161</v>
+        <v>0.9999906400717791</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7527118982886535</v>
+        <v>0.9999984735084139</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8240233214050341</v>
+        <v>0.9999934125685327</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02006297043783574</v>
+        <v>2.234272152830837e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2313730423788417</v>
+        <v>0.1726483162983586</v>
       </c>
       <c r="I26" t="n">
-        <v>0.004479354451228942</v>
+        <v>1.028968216088851e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1204705678637668</v>
+        <v>8.134419245847018e-07</v>
       </c>
       <c r="K26" t="n">
-        <v>0.06247496115749785</v>
+        <v>5.551901864969685e-06</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02784354366319164</v>
+        <v>0.001747547950620214</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1416438153885857</v>
+        <v>0.00472680881021312</v>
       </c>
       <c r="N26" t="n">
-        <v>1.015598313170024</v>
+        <v>1.000017370746199</v>
       </c>
       <c r="O26" t="n">
-        <v>0.147673885852797</v>
+        <v>0.004928038847107037</v>
       </c>
       <c r="P26" t="n">
-        <v>159.8177588595039</v>
+        <v>173.4180198972633</v>
       </c>
       <c r="Q26" t="n">
-        <v>252.4523215494872</v>
+        <v>266.0525825872466</v>
       </c>
     </row>
   </sheetData>
